--- a/mistral_translate_work/split_by_prompt/excel/system_text/lang_mail/lang_mail__system_text__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/system_text/lang_mail/lang_mail__system_text__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Thư</t>
         </is>
       </c>
     </row>
